--- a/data/trans_orig/RUIDO_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29491</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>47583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>21049</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33599</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19889</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34489</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>44109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63349</t>
+          <t>62724</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,47 +1914,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>18493</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>11974</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>25670</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>8,8%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>18493</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>12575</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>25684</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>30798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>26624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48757</t>
+          <t>48127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27553</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43277</t>
+          <t>44374</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45746</t>
+          <t>46233</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67058</t>
+          <t>66628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17972</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>16936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32548</t>
+          <t>35273</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21267</t>
+          <t>22247</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21037</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80450</t>
+          <t>86645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>26711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37798</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>118004</t>
+          <t>127821</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51306</t>
+          <t>50744</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43754</t>
+          <t>43976</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>65472</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>61323</t>
+          <t>57817</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>108961</t>
+          <t>109004</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>25149</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16263</t>
+          <t>17251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>37893</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23564</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139688</t>
+          <t>133228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>83941</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>122321</t>
+          <t>122257</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>212552</t>
+          <t>213062</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>61501</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108560</t>
+          <t>109571</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109333</t>
+          <t>107996</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>140198</t>
+          <t>138537</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>180617</t>
+          <t>178196</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>239089</t>
+          <t>237279</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41481</t>
+          <t>42671</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>56497</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>92100</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>45477</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>48869</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77968</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>706</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>851</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3782</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6596</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6898</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10456</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5521</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8197</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>38,24%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>56,77%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7767</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4944</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11072</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>47,77%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19690</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5775</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5132</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2418</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8337</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2943</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2651</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5410</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,44%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14438</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14438</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14438</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23177</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23177</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23177</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>41598</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41598</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41598</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7137</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3908</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11753</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4281</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8889</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19803</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14477</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25626</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14030</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9093</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21197</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>24,04%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>36,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30985</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>37876</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29181</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47583</t>
+          <t>38655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22973</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17387</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30107</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>44,63%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27214</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>21049</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33663</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>46,64%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>57,69%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33600</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>53321</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44109</t>
+          <t>40374</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62724</t>
+          <t>57548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7571</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3674</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12736</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5547</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10018</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20585</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9974</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5601</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15586</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7284</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4141</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13213</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,27 +1929,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25670</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>67458</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>67458</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>67458</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>58355</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>58355</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>58355</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>136125</t>
+          <t>119318</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>136125</t>
+          <t>119318</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136125</t>
+          <t>119318</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13133</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5278</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10348</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18562</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19926</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13765</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28357</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>14228</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8480</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23340</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22305</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30798</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>31902</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26624</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48127</t>
+          <t>41903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>34832</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>26156</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>43127</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>43,06%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>32,34%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>53,32%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>20685</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>15006</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>27207</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>34,92%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,34%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44374</t>
+          <t>27576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>56428</t>
+          <t>56012</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46233</t>
+          <t>45348</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66628</t>
+          <t>66911</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>48,0%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14725</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8981</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>22922</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>28,34%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10788</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5731</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>16039</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24875</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35285</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12084</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>13945</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,55%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>22073</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>80884</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>80884</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>80884</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>59226</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>59226</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>59226</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>143179</t>
+          <t>139411</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>143179</t>
+          <t>139411</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>143179</t>
+          <t>139411</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12484</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3106</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14862</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>23687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17393</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>10988</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>24660</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>24,05%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>44928</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>21947</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>86645</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>19,05%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>75,22%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>21557</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>30935</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>63517</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127821</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>50949</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>41726</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>59907</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>49,7%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>40,7%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>58,43%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>36469</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>14110</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>50744</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>31,66%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>44,05%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54618</t>
+          <t>35547</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43976</t>
+          <t>27707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65472</t>
+          <t>43724</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>91087</t>
+          <t>86496</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57817</t>
+          <t>72780</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>109004</t>
+          <t>98188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>17990</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11781</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>26495</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>25,84%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>10022</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>16899</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25149</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>27261</t>
+          <t>28533</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17251</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>38942</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5011</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>17243</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>16,82%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>15524</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>6403</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>23187</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>22571</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>26208</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>36079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>102521</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>102521</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>102521</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106733</t>
+          <t>92653</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>106733</t>
+          <t>92653</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106733</t>
+          <t>92653</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>221925</t>
+          <t>195175</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>221925</t>
+          <t>195175</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>221925</t>
+          <t>195175</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>13761</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>18535</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>11043</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>27525</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>40020</t>
+          <t>38688</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52840</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>60904</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>49828</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>74161</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>80084</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>55157</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>133228</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>31,29%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>52,05%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>69497</t>
+          <t>49985</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83941</t>
+          <t>60425</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>149581</t>
+          <t>110889</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>122257</t>
+          <t>96899</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213062</t>
+          <t>128802</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>114274</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>101455</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>129627</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>38,24%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>48,86%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>92135</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>61501</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>109571</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>42,81%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>123418</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107996</t>
+          <t>76759</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138537</t>
+          <t>100597</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>215553</t>
+          <t>203628</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>178196</t>
+          <t>183742</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>237279</t>
+          <t>220710</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>43433</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>33970</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>56378</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>21,25%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>31489</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>21105</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>42671</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56497</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>75281</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59626</t>
+          <t>61414</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>92100</t>
+          <t>89110</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>27227</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>18777</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>37628</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>33707</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>22836</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>45477</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>17,77%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>62982</t>
+          <t>60742</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>76545</t>
+          <t>74122</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>350</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
